--- a/data/trans_orig/IP31B_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_R_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33771</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25459</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43206</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34506</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27678</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42719</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>35107</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>27252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>45173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>57617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94676</t>
+          <t>80283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86532</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77097</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>94844</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>79745</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>71532</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>86573</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90283</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101600</t>
+          <t>91346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>170027</t>
+          <t>170023</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152575</t>
+          <t>158618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184314</t>
+          <t>181284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75443</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63468</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>92179</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>64429</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52378</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>78977</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87602</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72943</t>
+          <t>45385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103204</t>
+          <t>66876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>152031</t>
+          <t>131816</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132630</t>
+          <t>114728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172996</t>
+          <t>149621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>155798</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>139062</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>167773</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>120898</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106350</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>132949</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159918</t>
+          <t>123542</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144316</t>
+          <t>113039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174577</t>
+          <t>134530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280816</t>
+          <t>279340</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259851</t>
+          <t>261535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300217</t>
+          <t>296428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>185327</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>185327</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>185327</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>432847</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>432847</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>432847</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64936</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53326</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77880</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78853</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56290</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121924</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73836</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>65770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>118158</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128306</t>
+          <t>102707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207465</t>
+          <t>135811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101287</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88343</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>112897</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>107333</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64262</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129896</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108857</t>
+          <t>100051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95259</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121472</t>
+          <t>109648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>216190</t>
+          <t>201338</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161415</t>
+          <t>183685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240574</t>
+          <t>216789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>153273</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>153273</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>153273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>368880</t>
+          <t>319496</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>368880</t>
+          <t>319496</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>368880</t>
+          <t>319496</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51708</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42327</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>60955</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41939</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32342</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51174</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54993</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65948</t>
+          <t>48022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>96932</t>
+          <t>90810</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83090</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112513</t>
+          <t>105235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>113513</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>104266</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>122894</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>121496</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>112261</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>131093</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>121346</t>
+          <t>123689</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>114769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131475</t>
+          <t>132108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>242841</t>
+          <t>237202</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227260</t>
+          <t>222777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256683</t>
+          <t>249414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165221</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>165221</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>165221</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>163435</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>163435</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>163435</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>339773</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>339773</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>339773</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>225858</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>204522</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>250878</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>219727</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>192703</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>282508</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>165303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>203868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>440688</t>
+          <t>380431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>541957</t>
+          <t>441822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>457130</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>432110</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>478466</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>429472</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>366691</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>456496</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>480404</t>
+          <t>430773</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451139</t>
+          <t>410708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505945</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>909876</t>
+          <t>887903</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846795</t>
+          <t>855743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>948064</t>
+          <t>917134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
